--- a/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
+++ b/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alias Master" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Required" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Matches" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapping Audit" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer Master'!$A$1:$B$110</definedName>
@@ -447,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B110"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -455,1322 +456,1562 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Customer ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Official Customer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>C001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Aacs Engineering</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>C002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Aadesh Engineering</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>C003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Aashirwad Hi Tech Engineering</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>C004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>ACE Inotec MFG.Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>C005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Advik Hi-Tech Pvt.Ltd-Chakan</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>C006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Amol Auto Parts</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>C007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Amphenol FCI India Ltd.</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Amphenol FCI India Ltd.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>C008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>ANAND I-POWER LTD.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>C009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Anu Industries</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>C010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Ascent Casting Technologies</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>C011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Atul Enterprises</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>C012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Auto Line</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>C013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Avadhoot Engineering</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>C014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Axletech India Ltd.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>C015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Bharat Forge Ltd</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>C016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Bharti Thermal</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>C017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Bhushan Steel</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>C018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Brakes India</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>C019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Bright Precision Machining Works Pvt Ltd.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>C020</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Cando Tech India</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>C021</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Cenvision Technocraft</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>C022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>CIE Automotive</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>C023</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Clips India</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>C024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Dana Anand India Ltd.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>C025</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>DAS Autotech India Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>C026</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Davi Engineering Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>C028</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Dunung Ind</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Egearz Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>C030</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Endurance Technologies Ltd.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>C031</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>FCI Oen</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>C032</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Flash Electronics (I) Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>C033</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Four Star Industries</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>C034</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Gala Precision</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>C035</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Ganesh Industries</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>C036</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Gear Control</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>C037</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>GKN driveline Pune</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>C039</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Harsha Engineers International Ltd</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>C040</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Helical auto technology</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>C041</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Hermino India Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>C042</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Hirschvogel Components India</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>C043</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>HTF ACD GKN</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>C044</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>HTF ACD Nexteer</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>C045</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>HTF ACD-Exedy</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>C046</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>HTF ACD-Hyundai Wia</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>C047</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>JAL Precision (Jagadamba Auto Comp.)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>C048</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Jaya-Hind Industries Ltd.Pune</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>C049</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Joinvel  Products</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Joinvel Products</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>C050</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Kharghar Metal Reforming Ind.Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>C051</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Kotecha Steel Forge And Ind. Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>C052</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Lucy Electric Mfg. &amp; Technologies India Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>C053</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>M D Industries</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>C054</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Madras Engineering Industries Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>C055</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Mahabal Metal Pvt.Ltd</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>C056</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Mahabal Metal Pvt.Ltd</t>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C057</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Master Gasket Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>C057</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Master Gasket Pvt.Ltd.</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C058</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mauli Engineering Works</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>C058</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Mauli Engineering Works</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C059</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Memco Engineering Pvt Ltd.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>C059</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Memco Engineering Pvt Ltd.</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C060</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Meritech</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>C060</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Meritech</t>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C061</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Metalyst Forging Ltd</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>C061</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Metalyst Forging Ltd</t>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C062</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Monocraft Forge and Machining</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>C062</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Monocraft Forge and Machining</t>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C063</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Mubea Automotive Components India Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>C063</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Mubea Automotive Components India Pvt.Ltd.</t>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C064</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Mudhra Fine Blanc Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>C064</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Mudhra Fine Blanc Pvt Ltd</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C065</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>National Engineering Ind.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>C065</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>National Engineering Ind.Ltd.</t>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C066</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>OBSC Perfection Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>C066</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>OBSC Perfection Pvt. Ltd.</t>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C067</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Om Sai Industries</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>C067</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Om Sai Industries</t>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C068</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OSR Gears</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>C068</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>OSR Gears</t>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C069</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Piano Presitel</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>C069</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Piano Presitel</t>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C070</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pinakin Fasterns</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>C070</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Pinakin Fasterns</t>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C071</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Porite India Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>C071</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Porite India Pvt. Ltd.</t>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C072</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pressmech Engineering</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>C072</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>Pressmech Engineering</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C073</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Prime Sintek Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>C073</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Prime Sintek Pvt.Ltd.</t>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C074</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PTI Engineering Technologies Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>C074</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>PTI Engineering Technologies Pvt. Ltd.</t>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C075</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PYG Engineering</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>C075</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>PYG Engineering</t>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C076</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Randack Fasteners India Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>C076</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Randack Fasteners India Pvt. Ltd.</t>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C077</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Rapid Machining Tech.Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>C077</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Rapid Machining Tech.Pvt.Ltd.</t>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C078</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Sahayog Nirmitee</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>C078</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Sahayog Nirmitee</t>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C080</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Samarth Precision</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>C079</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Sahayog Nirmitee</t>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C081</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Sanjeev Auto Parts</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>C080</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Samarth Precision</t>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C082</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Saptashrungi Products Links</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>C081</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Auto Parts</t>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C083</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>C082</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>Saptashrungi Products Links</t>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C084</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Shefield Technoplast Pvt.Ltd</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>C083</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>Schaeffler India Ltd.</t>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C085</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Shree Balaji Engineering</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>C084</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>Shefield Technoplast Pvt.Ltd</t>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C086</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shree Pressing</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>C085</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Shree Balaji Engineering</t>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>C087</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Sidhakala Engineers</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>C086</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Shree Pressing</t>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>C088</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SKF India Ltd.Pune</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>C087</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Sidhakala Engineers</t>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>C089</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>C088</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>SKF India Ltd.Pune</t>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>C090</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Spectrum Electric Industries Ltd</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>C089</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>C091</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SPI Auto India Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>C090</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>Spectrum Electric Industries Ltd</t>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>C092</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SQF TOTAL</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>C091</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>SPI Auto India Pvt. Ltd.</t>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>C093</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Square Engineering</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>C092</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>SQF TOTAL</t>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>C094</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Star Circlips &amp; Engg.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>C093</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>Square Engineering</t>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>C095</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Sundram Fasteners Ltd - Hosur</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>C094</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Star Circlips &amp; Engg.Ltd.</t>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C096</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Takshi Auto components</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>C095</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Sundram Fasteners Ltd - Hosur</t>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>C097</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tata precesion</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>C096</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>Takshi Auto components</t>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>C098</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Terminal Technologies</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>C097</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Tata precesion</t>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>C099</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Texmo Blank</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>C098</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>Terminal Technologies</t>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>C100</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tries Automation</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>C099</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>Texmo Blank</t>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>C101</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Uni-Tech CNC Centre Pvt Ltd</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>C100</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>Tries Automation</t>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>C102</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Unitech Industries-Aurangabad</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>C101</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Uni-Tech CNC Centre Pvt Ltd</t>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>C103</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Vaibhav Auto Parts</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>C102</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>Unitech Industries-Aurangabad</t>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>C104</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Varroc Engineering Pvt.Ltd.Pune</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>C103</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Vaibhav Auto Parts</t>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>C105</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Velkommen Engg</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>C104</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>Varroc Engineering Pvt.Ltd.Pune</t>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>C106</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Venkatesh Automobile Pvt.Ltd.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>C105</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Velkommen Engg</t>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>C107</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Vishal Engineers Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>C106</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>C108</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Western India Forgings Pvt. Ltd.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>C107</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>Vishal Engineers Pvt. Ltd.</t>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>C109</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Yash Industries</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>C108</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Western India Forgings Pvt. Ltd.</t>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>C110</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ASSOCIATED MFG LLP</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>C109</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Yash Industries</t>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>DUNUNG INDUSTRIES PVT.LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FLASH VIVEN MACHINING TECHNOLOGIES PVT. LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>C113</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GKN DRIVELINE LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>C114</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SONA BLW PRECISION FORGINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>C115</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VARROC ENGINEERING LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>C116</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>HELICAL AUTO TECHNOLOGY INDIA PVT.LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>C117</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NATIONAL ENGINEERING INDUSTRIES LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>C118</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEMS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>C119</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PRESMECH ENGINEERING PVT.LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>C120</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SKF INDIA LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>C121</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SUNDRAM FASTENERS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>C122</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>JAYA HIND INDUSTRIES PVT LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>C123</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>L.G.BALAKRISHNAN &amp; BROS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>C124</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEMS PVT LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>C125</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; BOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>C126</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MAHINDRA CIE AUTOMOTIVE LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>C127</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PRIME SINTEK PVT.LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>C128</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RAPID MACHINING TECHNOLOGIES PVT LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>C129</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SPECIALITY SINTERED PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>C130</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>VENKATESH AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>C131</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>VISHAL ENGINEERS PVT.LTD</t>
         </is>
       </c>
     </row>
@@ -1786,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1796,2325 +2037,1671 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Alias</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>Customer ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Official Customer</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Alias</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Match Score</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACE INOTEC MANUFACTURING PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>C004</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>ACE Inotec MFG.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>ACE INOTEC MANUFACTURING PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADVIK HI-TECH PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>C005</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Advik Hi-Tech Pvt.Ltd-Chakan</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ADVIK HI-TECH PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADVIK HI-TECH-PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>C005</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Advik Hi-Tech Pvt.Ltd-Chakan</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ADVIK HI-TECH-PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADVIK HII-TECH PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>C005</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Advik Hi-Tech Pvt.Ltd-Chakan</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ADVIK HII-TECH PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>90</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADVIK-HI-TECH PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>C005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Advik Hi-Tech Pvt.Ltd-Chakan</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ADVIK-HI-TECH PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BRAKES INDIA PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>C018</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Brakes India</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BRAKES INDIA PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BRIGHT PRECISION MACHINING WORKS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>C019</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Bright Precision Machining Works Pvt Ltd.</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BRIGHT PRECISION MACHINING WORKS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BRIGIHT PRECISION MACHINING WORKS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>C019</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Bright Precision Machining Works Pvt Ltd.</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>BRIGIHT PRECISION MACHINING WORKS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>98.8</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIE AUTOMOTIVE INDIA LTD</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>C022</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>CIE Automotive</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>CIE AUTOMOTIVE INDIA LTD</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MAHINDRA CIE AUTOMOTIVE LTD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>C022</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>CIE Automotive</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>MAHINDRA CIE AUTOMOTIVE LTD</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DAVI ENGINEERING PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>C026</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Davi Engineering Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>DAVI ENGINEERING PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DAVI ENGINEERING PVT LTD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>C026</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Davi Engineering Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>DAVI ENGINEERING PVT LTD</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DIVGI TOEQTRANSFER SYSTEM PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TOEQTRANSFER SYSTEM PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>95.5</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DIVGI TOROTRANSFER SYSTEMS LTD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TOROTRANSFER SYSTEMS LTD</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DIVGI TOROTRANSFER SYSTEMS PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TOROTRANSFER SYSTEMS PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DIVGI TOROTRANSFER SYSTEMS PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TOROTRANSFER SYSTEMS PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFEF.-SYSTEMS PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFEF.-SYSTEMS PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEM LTD</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFER SYSTEM LTD</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEM PVTLTD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFER SYSTEM PVTLTD</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEMS LTD</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFER SYSTEMS LTD</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEMS PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFER SYSTEMS PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEMS PVT.' LTD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFER SYSTEMS PVT.' LTD</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEMS PVT.'LTD</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFER SYSTEMS PVT.'LTD</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DIVGI TORQTRANSFER SYSTEMSPVT. LTD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TORQTRANSFER SYSTEMSPVT. LTD</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>89.59999999999999</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DIVGI TOSQTRANSFER SYSTEMS PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>DIVGI TOSQTRANSFER SYSTEMS PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DIVGITORQTRANSFER SYSTEMS LTD</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>DIVGITORQTRANSFER SYSTEMS LTD</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DIVGITORQTRANSFER SYSTEMS PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>DIVGITORQTRANSFER SYSTEMS PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>98.5</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SYSTEMS PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>SYSTEMS PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TORQTRANSFER SYSTEMS PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>C027</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Divgi Torqtransfer Systems Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>TORQTRANSFER SYSTEMS PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ECEARZ PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Egearz Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>ECEARZ PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EGEAR.Z PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Egearz Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>EGEAR.Z PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>96.59999999999999</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EGEAR2 PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Egearz Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>EGEAR2 PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EGEARZ PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Egearz Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>EGEARZ PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EGEARZPVT. LTD</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Egearz Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>EGEARZPVT. LTD</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>96.3</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FGEARZ PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Egearz Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>FGEARZ PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GEARZF'VT.LTD</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>C029</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Egearz Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>GEARZF'VT.LTD</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ENDURANCE TECHNOLOGIES LTD</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>C030</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Endurance Technologies Ltd.</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>ENDURANCE TECHNOLOGIES LTD</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FCI OEN CONNECTORS LTD</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>C031</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>FCI Oen</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>FCI OEN CONNECTORS LTD</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>BOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GODREI &amp; BOYCE MFG. CO LTD</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>GODREI &amp; BOYCE MFG. CO LTD</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>89.7</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GODREI &amp; BOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>GODREI &amp; BOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>89.7</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GODREI&amp; BOYCE MFG..CO. LTD</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>GODREI&amp; BOYCE MFG..CO. LTD</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>89.7</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; BOYCE MFG. CD. LTD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; BOYCE MFG. CD. LTD</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; BOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; BOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; BOYCE MFG. CO._LTD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; BOYCE MFG. CO._LTD</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; BOYCE MFG. CO_LTD</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; BOYCE MFG. CO_LTD</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; BOYCE MFG.CO. LTD</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; BOYCE MFG.CO. LTD</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; BOYCEMFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; BOYCEMFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>91.2</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; DOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; DOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>89.7</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GODREJ &amp; SOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp; SOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>89.7</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>GODREJ &amp;-BOYEERMFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp;-BOYEERMFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>86.2</v>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GODREJ &amp;. BOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ &amp;. BOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GODREJ&amp;BOYCEIMFG.CO. LTD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>GODREJ&amp;BOYCEIMFG.CO. LTD</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>89.7</v>
-      </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GODREJI &amp; BOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>GODREJI &amp; BOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>91.5</v>
-      </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GOREJ &amp; BOYCE MFG. CO. LTD</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>C038</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Godrej &amp; Boyce Mfg. Co. Ltd. - Goa</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>GOREJ &amp; BOYCE MFG. CO. LTD</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>91.2</v>
-      </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HELICAL AUTO TECHNOLOGY INDIA PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>C040</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Helical auto technology</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>HELICAL AUTO TECHNOLOGY INDIA PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>JAYA HIND INDUSTRIES PVT LTD</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>C048</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Jaya-Hind Industries Ltd.Pune</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>JAYA HIND INDUSTRIES PVT LTD</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>92.3</v>
-      </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>KOTECHA STEEL FORGE AND CAST IND.PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>C051</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Kotecha Steel Forge And Ind. Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>KOTECHA STEEL FORGE AND CAST IND.PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IGW INDIA TECHNOLOGIES PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>C052</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Lucy Electric Mfg. &amp; Technologies India Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>IGW INDIA TECHNOLOGIES PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LUCY ELECTRIC MFG. &amp; TECHNOLOGIES INDIA PVT LTD</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>C052</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Lucy Electric Mfg. &amp; Technologies India Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>LUCY ELECTRIC MFG. &amp; TECHNOLOGIES INDIA PVT LTD</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LUCY ELECTRIC MIFG. &amp; TECHNOLOGIES INDIA PVT LTD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>C052</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Lucy Electric Mfg. &amp; Technologies India Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>LUCY ELECTRIC MIFG. &amp; TECHNOLOGIES INDIA PVT LTD</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>99</v>
-      </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MADRAS ENGINEERING INDUSTRIES PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>C054</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Madras Engineering Industries Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>MADRAS ENGINEERING INDUSTRIES PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MASTER GASKET PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>C057</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Master Gasket Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>MASTER GASKET PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MASTER GASKET-PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>C057</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Master Gasket Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>MASTER GASKET-PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MASTES GASKET PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>C057</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Master Gasket Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>MASTES GASKET PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>95.2</v>
-      </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MEMCO ENGINEERING PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>C059</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Memco Engineering Pvt Ltd.</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>MEMCO ENGINEERING PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>METALYST FORGING LTD</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>C061</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Metalyst Forging Ltd</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>METALYST FORGING LTD</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>METALYST FORSINGLTD</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>C061</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Metalyst Forging Ltd</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>METALYST FORSINGLTD</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>92.3</v>
-      </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MUBEA AUTOMOTIVE COMPONENTS INDIA PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>C063</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Mubea Automotive Components India Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>MUBEA AUTOMOTIVE COMPONENTS INDIA PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PTI ENGINEERING TECHNOLOGIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>C074</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>PTI Engineering Technologies Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>PTI ENGINEERING TECHNOLOGIES PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PTI ENGINIEERING TECHNOLOGIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>C074</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>PTI Engineering Technologies Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>PTI ENGINIEERING TECHNOLOGIES PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PTIENGINEERING TECHNOLOGIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>C074</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>PTI Engineering Technologies Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>PTIENGINEERING TECHNOLOGIES PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>90.09999999999999</v>
-      </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PTTENGINEERINGTECHNOLOGIES PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>C074</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>PTI Engineering Technologies Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>PTTENGINEERINGTECHNOLOGIES PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PDRITE INDIA PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>C071</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Porite India Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>PDRITE INDIA PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>95</v>
-      </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PORITE INDIA PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>C071</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Porite India Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>PORITE INDIA PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PRIME SINTEK PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>C073</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Prime Sintek Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>PRIME SINTEK PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PRIME SINTER-PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>C073</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Prime Sintek Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>PRIME SINTER-PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>95</v>
-      </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>RANDACK FASTENERS INDIA PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>C076</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Randack Fasteners India Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>RANDACK FASTENERS INDIA PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>RAPID MACHINING TECHINOLOGIES PVT LTD</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
         <is>
           <t>C077</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Rapid Machining Tech.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>RAPID MACHINING TECHINOLOGIES PVT LTD</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="n">
-        <v>90.2</v>
-      </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>RAPID MACHINING TECHNOLOGIES PVT LTD</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>C077</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Rapid Machining Tech.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>RAPID MACHINING TECHNOLOGIES PVT LTD</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="n">
-        <v>90.2</v>
-      </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>RAPID MACHININGTECHNOLOGIES PVT LTD</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>C077</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>Rapid Machining Tech.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>RAPID MACHININGTECHNOLOGIES PVT LTD</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>85.7</v>
-      </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SKF INDIA LTD</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>C088</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>SKF India Ltd.Pune</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>SKF INDIA LTD</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SKF INDIA.LTD</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>C088</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>SKF India Ltd.Pune</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>SKF INDIA.LTD</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>HELICAL AUTO TECHINOLOGY INDIA PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>C091</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>SPI Auto India Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>HELICAL AUTO TECHINOLOGY INDIA PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>90</v>
-      </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SCHAEFFLER INDIA LTD</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>C083</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Schaeffler India Ltd.</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>SCHAEFFLER INDIA LTD</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SHEFIELD TECHNOPLAST PVT LTD</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>C084</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>Shefield Technoplast Pvt.Ltd</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>SHEFIELD TECHNOPLAST PVT LTD</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SHEFIELDITEEHNDPEAST PVT LTD</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>C084</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Shefield Technoplast Pvt.Ltd</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>SHEFIELDITEEHNDPEAST PVT LTD</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="n">
-        <v>85.7</v>
-      </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SFECIALITY SINTERED PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>SFECIALITY SINTERED PRODUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="n">
-        <v>91.2</v>
-      </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SPECIALITY SINFERED PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>SPECIALITY SINFERED PRODUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="n">
-        <v>91.2</v>
-      </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SPECIALITY SINTERED PRGDUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>SPECIALITY SINTERED PRGDUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="n">
-        <v>91.5</v>
-      </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SPECIALITY SINTERED PRO.PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>SPECIALITY SINTERED PRO.PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SPECIALITY SINTERED PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>SPECIALITY SINTERED PRODUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SPECIALITY SINTERED-PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>SPECIALITY SINTERED-PRODUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SPECIALITY SINTERED.PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>SPECIALITY SINTERED.PRODUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="n">
-        <v>94.09999999999999</v>
-      </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SPECIAUITY SINTERED PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>SPECIAUITY SINTERED PRODUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="n">
-        <v>91.2</v>
-      </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SRECIALITY SINTERED PRODUCTS PVT LTD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>C089</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>Speciality Sintered Prod.Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>SRECIALITY SINTERED PRODUCTS PVT LTD</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
-        <v>91.2</v>
-      </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SUNDRAM FASTENERS LTD</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>C095</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Sundram Fasteners Ltd - Hosur</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>SUNDRAM FASTENERS LTD</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VARROC ENGINEERING LTD</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
         <is>
           <t>C104</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>Varroc Engineering Pvt.Ltd.Pune</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>VARROC ENGINEERING LTD</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>VENIKATESH -AUTOMOBILE-PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>VENIKATESH -AUTOMOBILE-PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="n">
-        <v>98.2</v>
-      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>VENIKATESH AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>VENIKATESH AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="n">
-        <v>98.2</v>
-      </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>VENIKATFSH AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>VENIKATFSH AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="n">
-        <v>94.7</v>
-      </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>VENKAFESH AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>VENKAFESH AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>96.40000000000001</v>
-      </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>VENKATBSH-AUTOMOBILEIPVT. LTD</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>VENKATBSH-AUTOMOBILEIPVT. LTD</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>VENKATESH AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>VENKATESH AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>VENKATESH AUTOMOBILE PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>VENKATESH AUTOMOBILE PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>VENKATESH AUTOMOEILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>VENKATESH AUTOMOEILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="n">
-        <v>96.40000000000001</v>
-      </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>VENKATESH AUTOMOGILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>VENKATESH AUTOMOGILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
-        <v>96.40000000000001</v>
-      </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>VENKATESH A_JTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>VENKATESH A_JTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="n">
-        <v>94.7</v>
-      </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>VENKATESH-AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>VENKATESH-AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>VENKATESH-AUTOMOBILEPVT. LTD</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>VENKATESH-AUTOMOBILEPVT. LTD</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>98.2</v>
-      </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>VENKAYESH AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>VENKAYESH AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="n">
-        <v>96.40000000000001</v>
-      </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>VUBNKATESH AUTOMOBILE PVT. LTD</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
         <is>
           <t>C106</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>Venkatesh Automobile Pvt.Ltd.</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>VUBNKATESH AUTOMOBILE PVT. LTD</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="n">
-        <v>94.7</v>
-      </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>VISHAL ENGINEERS PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
         <is>
           <t>C107</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>Vishal Engineers Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>VISHAL ENGINEERS PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>WESTERN INDIA FORGINGS PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
         <is>
           <t>C108</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Western India Forgings Pvt. Ltd.</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>WESTERN INDIA FORGINGS PVT.LTD</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="n">
-        <v>100</v>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>GKN DRIVELINE (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>GKN Driveline India Limited</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>GKN DRIVELINE INDIA LTD</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>GKy Driyeline Indla Limited</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>GIKN Driveline India Limited</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>GKN Priveline India Limited</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KN Driveline India Limited</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>GXN Driveline India Limited</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>KN DRIVELINE INDIA LTD</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>GKN Drivaline India Limited</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>GKN DRIVEUNE (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SKN Driveline India Limited</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>C037</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Nexteer Automotive India Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NEXTEER AUTOMOTIVE INDIA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Nexteer Automotive Inaia Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Nexteer Automotive India Pyt. Ltd</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>lexteer Automotive India Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>exteer Automotive India Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>C044</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Exedy India Limited</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>C045</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Hyundai Wia India Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>C046</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>DUNUNG INDUSTRIES PVT.LTD</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>C028</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>NATIONAL ENGINEERING INDUSTRIES LTD</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>C065</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TATA PRECISION INDUSTRIES (INDIA) LTD</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>C097</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -19780,4 +19367,80 @@
   <autoFilter ref="A1:I268"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Existing customers</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Existing aliases</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Final aliases</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Confirmed aliases added</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Missing referenced Customer IDs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alias conflicts requiring client decision</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
+++ b/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Master" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alias Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Required" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Matches" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapping Audit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Customer Master" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Alias Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Review Required" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Matches" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mapping Audit" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer Master'!$A$1:$B$110</definedName>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2012,6 +2012,18 @@
       <c r="B130" t="inlineStr">
         <is>
           <t>VISHAL ENGINEERS PVT.LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>C132</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Nexteer Automotive India Pvt. Ltd</t>
         </is>
       </c>
     </row>

--- a/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
+++ b/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2012,18 +2012,6 @@
       <c r="B130" t="inlineStr">
         <is>
           <t>VISHAL ENGINEERS PVT.LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>C132</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Nexteer Automotive India Pvt. Ltd</t>
         </is>
       </c>
     </row>

--- a/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
+++ b/invoice_sorter_app_v2/customer_master_alias_mapping.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:B131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2012,6 +2012,18 @@
       <c r="B130" t="inlineStr">
         <is>
           <t>VISHAL ENGINEERS PVT.LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>C132</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Nexteer Automotive India Pvt. Ltd</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3592,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>C044</t>
+          <t>C132</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3604,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>C044</t>
+          <t>C132</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3616,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>C044</t>
+          <t>C132</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3628,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>C044</t>
+          <t>C132</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3640,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>C044</t>
+          <t>C132</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3652,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>C044</t>
+          <t>C132</t>
         </is>
       </c>
     </row>
